--- a/therapist_forms/001_insomnia_questionnaire--therapist_forms.xlsx
+++ b/therapist_forms/001_insomnia_questionnaire--therapist_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'sometimes'}</t>
+          <t>sometimes</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Sometimes'}</t>
+          <t>Sometimes</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'often'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Often'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'usually'}</t>
+          <t>usually</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Usually'}</t>
+          <t>Usually</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'always'}</t>
+          <t>always</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Always'}</t>
+          <t>Always</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'not_at_all'}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Not at all'}</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'less_than_30_minutes'}</t>
+          <t>less_than_30_minutes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Less than 30 minutes'}</t>
+          <t>Less than 30 minutes</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'30-60_minutes'}</t>
+          <t>30-60_minutes</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': '30-60 minutes'}</t>
+          <t>30-60 minutes</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'61-120_minutes'}</t>
+          <t>61-120_minutes</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': '61-120 minutes'}</t>
+          <t>61-120 minutes</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'more_than_120_minutes'}</t>
+          <t>more_than_120_minutes</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'More than 120 minutes'}</t>
+          <t>More than 120 minutes</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'more_than_3_hours'}</t>
+          <t>more_than_3_hours</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'More than 3 hours'}</t>
+          <t>More than 3 hours</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'1_stage'}</t>
+          <t>1_stage</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': '1 stage'}</t>
+          <t>1 stage</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'2_stages'}</t>
+          <t>2_stages</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': '2 stages'}</t>
+          <t>2 stages</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'3_stages'}</t>
+          <t>3_stages</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': '3 stages'}</t>
+          <t>3 stages</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'4_stages'}</t>
+          <t>4_stages</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': '4 stages'}</t>
+          <t>4 stages</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'5_stages'}</t>
+          <t>5_stages</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': '5 stages'}</t>
+          <t>5 stages</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'6_stages'}</t>
+          <t>6_stages</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': '6 stages'}</t>
+          <t>6 stages</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfactory'}</t>
+          <t>very_satisfactory</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Very Satisfactory'}</t>
+          <t>Very Satisfactory</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'fairly_satisfactory'}</t>
+          <t>fairly_satisfactory</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Fairly Satisfactory'}</t>
+          <t>Fairly Satisfactory</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'unsatisfactory'}</t>
+          <t>unsatisfactory</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Unsatisfactory'}</t>
+          <t>Unsatisfactory</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'every_day'}</t>
+          <t>every_day</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Every Day'}</t>
+          <t>Every Day</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'2-3_times_per_week'}</t>
+          <t>2-3_times_per_week</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': '2-3 times per week'}</t>
+          <t>2-3 times per week</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'1_time_per_week'}</t>
+          <t>1_time_per_week</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': '1 time per week'}</t>
+          <t>1 time per week</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'not_at_all'}</t>
+          <t>not_at_all</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Not at all'}</t>
+          <t>Not at all</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'a_bit'}</t>
+          <t>a_bit</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'A bit'}</t>
+          <t>A bit</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'a_little'}</t>
+          <t>a_little</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'A little'}</t>
+          <t>A little</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat'}</t>
+          <t>somewhat</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat'}</t>
+          <t>Somewhat</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'a_lot'}</t>
+          <t>a_lot</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'A lot'}</t>
+          <t>A lot</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'extremely'}</t>
+          <t>extremely</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Extremely'}</t>
+          <t>Extremely</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfactory'}</t>
+          <t>very_satisfactory</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Very Satisfactory'}</t>
+          <t>Very Satisfactory</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'fairly_satisfactory'}</t>
+          <t>fairly_satisfactory</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'Fairly Satisfactory'}</t>
+          <t>Fairly Satisfactory</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1726,12 +1726,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'poor'}</t>
+          <t>poor</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'Poor'}</t>
+          <t>Poor</t>
         </is>
       </c>
     </row>
@@ -1743,12 +1743,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'label':_'unsatisfactory'}</t>
+          <t>unsatisfactory</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'label': 'Unsatisfactory'}</t>
+          <t>Unsatisfactory</t>
         </is>
       </c>
     </row>
